--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/white_4205_buckeyemail_osu_edu/Documents/Sp26 Semester/Sp26 Independant Study/Deliverables/XMLtoExcelGUI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_AB585A0FD57DF05E6D15C41540B8B6FF68BBF8DD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4470848-AB7A-4935-97B3-27A27570F678}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_AB5877AF5258BA5F6D15C41540B8B6FF68BBF8DD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5013D783-103A-45F9-8C3E-18C00D740A8B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -434,6 +434,9 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.88671875" bestFit="1" customWidth="1"/>
